--- a/data/gravel/Norco Search C gen 3 2025.xlsx
+++ b/data/gravel/Norco Search C gen 3 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEAFBC9-C43B-5748-A1DA-BE23F9063A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA790005-EF0E-734E-9A3A-E58445010FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>estimate 432</t>
+  </si>
+  <si>
+    <t>https://www.norco.com/cmsb/uploads/bikes/bikes/my26-search-c-force-axs-xplr-pistachio-green-shadow-main.webp</t>
   </si>
 </sst>
 </file>
@@ -775,6 +778,11 @@
         <v>92</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Norco Search C gen 3 2025.xlsx
+++ b/data/gravel/Norco Search C gen 3 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA790005-EF0E-734E-9A3A-E58445010FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F4E3A1-B9FA-D445-AAED-9DCF519E15C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7120" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,15 @@
   </si>
   <si>
     <t>https://www.norco.com/cmsb/uploads/bikes/bikes/my26-search-c-force-axs-xplr-pistachio-green-shadow-main.webp</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Port Coquitlam, British Columbia, Canada</t>
   </si>
 </sst>
 </file>
@@ -732,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1694,6 +1703,17 @@
       <c r="A75" t="s">
         <v>67</v>
       </c>
+      <c r="B75" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Norco Search C gen 3 2025.xlsx
+++ b/data/gravel/Norco Search C gen 3 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F4E3A1-B9FA-D445-AAED-9DCF519E15C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA27BA4-AAD6-064F-AC8A-88F73CD32CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7120" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27240" yWindow="-23020" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -353,15 +353,6 @@
     <t>S1</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
-    <t>a8:g35</t>
-  </si>
-  <si>
     <t>estimate 432</t>
   </si>
   <si>
@@ -375,6 +366,9 @@
   </si>
   <si>
     <t>Port Coquitlam, British Columbia, Canada</t>
+  </si>
+  <si>
+    <t>a8:g33</t>
   </si>
 </sst>
 </file>
@@ -741,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -789,7 +783,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -797,7 +791,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -808,19 +802,19 @@
         <v>96</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>103</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -831,19 +825,19 @@
         <v>79</v>
       </c>
       <c r="C9" s="5">
-        <v>445</v>
+        <v>385</v>
       </c>
       <c r="D9" s="5">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="E9" s="5">
         <v>415</v>
       </c>
       <c r="F9" s="5">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="G9" s="5">
-        <v>385</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -854,19 +848,19 @@
         <v>80</v>
       </c>
       <c r="C10" s="5">
-        <v>634</v>
+        <v>554</v>
       </c>
       <c r="D10" s="5">
-        <v>611</v>
+        <v>564</v>
       </c>
       <c r="E10" s="5">
         <v>587</v>
       </c>
       <c r="F10" s="5">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="G10" s="5">
-        <v>554</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -923,19 +917,19 @@
         <v>83</v>
       </c>
       <c r="C13" s="5">
-        <v>580</v>
+        <v>440</v>
       </c>
       <c r="D13" s="5">
-        <v>545</v>
+        <v>475</v>
       </c>
       <c r="E13" s="5">
         <v>510</v>
       </c>
       <c r="F13" s="5">
-        <v>475</v>
+        <v>545</v>
       </c>
       <c r="G13" s="5">
-        <v>440</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -946,19 +940,19 @@
         <v>84</v>
       </c>
       <c r="C14" s="5">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="D14" s="5">
-        <v>73.75</v>
+        <v>74.25</v>
       </c>
       <c r="E14" s="5">
         <v>74</v>
       </c>
       <c r="F14" s="5">
-        <v>74.25</v>
+        <v>73.75</v>
       </c>
       <c r="G14" s="5">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -969,19 +963,19 @@
         <v>85</v>
       </c>
       <c r="C15" s="5">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D15" s="5">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E15" s="5">
         <v>427.5</v>
       </c>
       <c r="F15" s="5">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G15" s="5">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1038,19 +1032,19 @@
         <v>88</v>
       </c>
       <c r="C18" s="5">
-        <v>633</v>
+        <v>539</v>
       </c>
       <c r="D18" s="5">
-        <v>608</v>
+        <v>559</v>
       </c>
       <c r="E18" s="5">
         <v>583</v>
       </c>
       <c r="F18" s="5">
-        <v>559</v>
+        <v>608</v>
       </c>
       <c r="G18" s="5">
-        <v>539</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1061,19 +1055,19 @@
         <v>89</v>
       </c>
       <c r="C19" s="5">
-        <v>1132</v>
+        <v>1037</v>
       </c>
       <c r="D19" s="5">
-        <v>1108</v>
+        <v>1056</v>
       </c>
       <c r="E19" s="5">
         <v>1082</v>
       </c>
       <c r="F19" s="5">
-        <v>1056</v>
+        <v>1108</v>
       </c>
       <c r="G19" s="5">
-        <v>1037</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1084,19 +1078,19 @@
         <v>90</v>
       </c>
       <c r="C20" s="5">
-        <v>824</v>
+        <v>691</v>
       </c>
       <c r="D20" s="5">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="E20" s="5">
         <v>758</v>
       </c>
       <c r="F20" s="5">
-        <v>725</v>
+        <v>791</v>
       </c>
       <c r="G20" s="5">
-        <v>691</v>
+        <v>824</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1107,19 +1101,19 @@
         <v>91</v>
       </c>
       <c r="C21" s="5">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="D21" s="5">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="E21" s="5">
         <v>135</v>
       </c>
       <c r="F21" s="5">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="G21" s="5">
-        <v>100</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1153,19 +1147,19 @@
         <v>94</v>
       </c>
       <c r="C23" s="5">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="D23" s="5">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="E23" s="5">
         <v>290</v>
       </c>
       <c r="F23" s="5">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="G23" s="5">
-        <v>210</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1199,19 +1193,19 @@
         <v>95</v>
       </c>
       <c r="C25" s="5">
-        <v>172.5</v>
+        <v>165</v>
       </c>
       <c r="D25" s="5">
-        <v>172.5</v>
+        <v>170</v>
       </c>
       <c r="E25" s="5">
         <v>170</v>
       </c>
       <c r="F25" s="5">
-        <v>170</v>
+        <v>172.5</v>
       </c>
       <c r="G25" s="5">
-        <v>165</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1225,7 +1219,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1275,16 +1269,16 @@
         <v>45</v>
       </c>
       <c r="D30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G30">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1298,16 +1292,16 @@
         <v>50</v>
       </c>
       <c r="D31">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E31">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G31">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1318,24 +1312,24 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <f>C34</f>
+        <f>C34*2.54</f>
         <v>154.94</v>
       </c>
       <c r="D32">
-        <f>AVERAGE(D34,C35)</f>
-        <v>163.82999999999998</v>
+        <f>D34*2.54</f>
+        <v>162.56</v>
       </c>
       <c r="E32">
-        <f t="shared" ref="E32:G32" si="0">AVERAGE(E34,D35)</f>
-        <v>171.45</v>
+        <f>E34*2.54</f>
+        <v>170.18</v>
       </c>
       <c r="F32">
-        <f t="shared" si="0"/>
-        <v>179.07</v>
+        <f>F34*2.54</f>
+        <v>177.8</v>
       </c>
       <c r="G32">
-        <f t="shared" si="0"/>
-        <v>186.69</v>
+        <f>G34*2.54</f>
+        <v>185.42000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -1346,308 +1340,272 @@
         <v>29</v>
       </c>
       <c r="C33">
-        <f>D32</f>
-        <v>163.82999999999998</v>
+        <f>C35*2.54</f>
+        <v>165.1</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:F33" si="1">E32</f>
-        <v>171.45</v>
+        <f>D35*2.54</f>
+        <v>172.72</v>
       </c>
       <c r="E33">
-        <f t="shared" si="1"/>
-        <v>179.07</v>
+        <f>E35*2.54</f>
+        <v>180.34</v>
       </c>
       <c r="F33">
-        <f t="shared" si="1"/>
-        <v>186.69</v>
+        <f>F35*2.54</f>
+        <v>187.96</v>
       </c>
       <c r="G33">
-        <f>G35</f>
+        <f>G35*2.54</f>
         <v>195.58</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C34">
-        <f>C36*2.54</f>
-        <v>154.94</v>
+        <v>61</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:G35" si="2">D36*2.54</f>
-        <v>162.56</v>
+        <v>64</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
+        <v>67</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
-        <v>177.8</v>
+        <v>70</v>
       </c>
       <c r="G34">
-        <f t="shared" si="2"/>
-        <v>185.42000000000002</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>107</v>
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
       </c>
       <c r="C35">
-        <f>C37*2.54</f>
-        <v>165.1</v>
+        <v>65</v>
       </c>
       <c r="D35">
-        <f t="shared" si="2"/>
-        <v>172.72</v>
+        <v>68</v>
       </c>
       <c r="E35">
-        <f t="shared" si="2"/>
-        <v>180.34</v>
+        <v>71</v>
       </c>
       <c r="F35">
-        <f t="shared" si="2"/>
-        <v>187.96</v>
+        <v>74</v>
       </c>
       <c r="G35">
-        <f t="shared" si="2"/>
-        <v>195.58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C36">
-        <v>61</v>
-      </c>
-      <c r="D36">
-        <v>64</v>
-      </c>
-      <c r="E36">
-        <v>67</v>
-      </c>
-      <c r="F36">
-        <v>70</v>
-      </c>
-      <c r="G36">
-        <v>73</v>
-      </c>
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37">
-        <v>65</v>
-      </c>
-      <c r="D37">
-        <v>68</v>
-      </c>
-      <c r="E37">
         <v>71</v>
-      </c>
-      <c r="F37">
-        <v>74</v>
-      </c>
-      <c r="G37">
-        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H38" s="2"/>
+        <v>73</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
+        <v>34</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46">
         <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="4"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
+        <v>59</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B66" s="4"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>75</v>
@@ -1655,64 +1613,50 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B68" s="4"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>2199</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B71">
+        <v>3199</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72">
-        <v>2199</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73">
-        <v>3199</v>
+        <v>67</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>112</v>
-      </c>
-      <c r="B76" t="s">
-        <v>113</v>
+        <v>109</v>
+      </c>
+      <c r="B74" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
